--- a/MANUAL_TESTING.xlsx
+++ b/MANUAL_TESTING.xlsx
@@ -109,7 +109,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -123,11 +123,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -158,6 +186,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -586,11 +616,11 @@
           <t>MODULE: AUTHENTICATION</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="15" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
@@ -610,7 +640,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -618,7 +648,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -638,7 +672,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -646,7 +680,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
@@ -666,7 +704,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -674,7 +712,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
@@ -694,7 +736,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -702,7 +744,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -722,7 +768,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -730,7 +776,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -738,11 +788,11 @@
           <t>MODULE: DASHBOARD</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -762,7 +812,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -770,7 +820,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -790,7 +844,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -798,7 +852,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -806,11 +864,11 @@
           <t>MODULE: CLIENT MANAGEMENT &amp; SCANNING</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="15" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -830,7 +888,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -838,7 +896,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -858,7 +920,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -866,7 +928,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -886,7 +952,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -894,7 +960,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
@@ -914,7 +984,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -922,7 +992,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -930,11 +1004,11 @@
           <t>MODULE: ASSET MANAGEMENT</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="15" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
@@ -954,7 +1028,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -962,7 +1036,11 @@
           <t>Saagr</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -982,7 +1060,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -990,7 +1068,11 @@
           <t>Saagr</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
@@ -1010,7 +1092,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -1018,7 +1100,11 @@
           <t>Saagr</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1026,11 +1112,11 @@
           <t>MODULE: LICENSE MANAGEMENT</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="15" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
@@ -1050,7 +1136,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1058,7 +1144,11 @@
           <t>Saagr</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -1078,7 +1168,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1086,7 +1176,11 @@
           <t>Saagr</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -1094,11 +1188,11 @@
           <t>MODULE: COMPLIANCE TRACKING</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="15" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
@@ -1118,7 +1212,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1126,7 +1220,11 @@
           <t>Saagr</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
@@ -1146,7 +1244,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -1154,7 +1252,11 @@
           <t>Saagr</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -1162,11 +1264,11 @@
           <t>MODULE: ALERT MANAGEMENT</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="15" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
@@ -1186,7 +1288,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -1194,7 +1296,11 @@
           <t>Saagr</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr"/>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
@@ -1214,7 +1320,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -1222,7 +1328,11 @@
           <t>Saagr</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -1230,11 +1340,11 @@
           <t>MODULE: INTELLIGENCE &amp; REPORTS</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="15" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
@@ -1254,7 +1364,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1262,7 +1372,11 @@
           <t>Mega</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr"/>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
@@ -1282,7 +1396,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1290,7 +1404,11 @@
           <t>Mega</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr"/>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
@@ -1310,7 +1428,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1318,7 +1436,11 @@
           <t>Mega</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr"/>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -1326,11 +1448,11 @@
           <t>MODULE: NOTIFICATIONS &amp; AUDIT</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="15" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
@@ -1350,7 +1472,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -1358,7 +1480,11 @@
           <t>Mega</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr"/>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
@@ -1378,7 +1504,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -1386,7 +1512,11 @@
           <t>Mega</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr"/>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -1394,11 +1524,11 @@
           <t>MODULE: CLIENT AGENT</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="15" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
@@ -1418,7 +1548,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -1426,7 +1556,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr"/>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
@@ -1446,7 +1580,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1454,7 +1588,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
@@ -1474,7 +1612,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -1482,7 +1620,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr"/>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
@@ -1502,7 +1644,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -1510,7 +1652,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr"/>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
@@ -1530,7 +1676,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -1538,7 +1684,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr"/>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -1546,11 +1696,11 @@
           <t>MODULE: WEBSOCKET &amp; REAL-TIME</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
+      <c r="B45" s="14" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="15" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
@@ -1570,7 +1720,7 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -1578,7 +1728,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr"/>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
@@ -1598,7 +1752,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -1606,7 +1760,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr"/>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
@@ -1626,7 +1784,7 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -1634,7 +1792,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr"/>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
@@ -1654,7 +1816,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
@@ -1662,7 +1824,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr"/>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
@@ -1670,11 +1836,11 @@
           <t>MODULE: HEALTH SCORING &amp; MONITORING</t>
         </is>
       </c>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="5" t="n"/>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="n"/>
+      <c r="B50" s="14" t="n"/>
+      <c r="C50" s="14" t="n"/>
+      <c r="D50" s="14" t="n"/>
+      <c r="E50" s="14" t="n"/>
+      <c r="F50" s="15" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
@@ -1694,7 +1860,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -1702,7 +1868,11 @@
           <t>Mega</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr"/>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
@@ -1722,7 +1892,7 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -1730,7 +1900,11 @@
           <t>Mega</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr"/>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -1738,11 +1912,11 @@
           <t>MODULE: API TESTING</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
+      <c r="B53" s="14" t="n"/>
+      <c r="C53" s="14" t="n"/>
+      <c r="D53" s="14" t="n"/>
+      <c r="E53" s="14" t="n"/>
+      <c r="F53" s="15" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
@@ -1762,7 +1936,7 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
@@ -1770,7 +1944,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
@@ -1790,7 +1968,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
@@ -1798,7 +1976,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -1818,7 +2000,7 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -1826,7 +2008,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr"/>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -1834,11 +2020,11 @@
           <t>MODULE: INTEGRATION TESTING</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
+      <c r="B57" s="14" t="n"/>
+      <c r="C57" s="14" t="n"/>
+      <c r="D57" s="14" t="n"/>
+      <c r="E57" s="14" t="n"/>
+      <c r="F57" s="15" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -1858,7 +2044,7 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -1866,7 +2052,11 @@
           <t>Full Team</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
@@ -1886,7 +2076,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
@@ -1894,7 +2084,11 @@
           <t>Full Team</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
@@ -1914,7 +2108,7 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
@@ -1922,7 +2116,11 @@
           <t>Full Team</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr"/>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
@@ -1942,7 +2140,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
@@ -1950,7 +2148,11 @@
           <t>Full Team</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr"/>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
@@ -1958,11 +2160,11 @@
           <t>MODULE: SECURITY TESTING</t>
         </is>
       </c>
-      <c r="B62" s="5" t="n"/>
-      <c r="C62" s="5" t="n"/>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="n"/>
+      <c r="B62" s="14" t="n"/>
+      <c r="C62" s="14" t="n"/>
+      <c r="D62" s="14" t="n"/>
+      <c r="E62" s="14" t="n"/>
+      <c r="F62" s="15" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
@@ -1982,7 +2184,7 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
@@ -1990,7 +2192,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
@@ -2010,7 +2216,7 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
@@ -2018,7 +2224,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
@@ -2038,7 +2248,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
@@ -2046,7 +2256,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr"/>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
@@ -2066,7 +2280,7 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
@@ -2074,7 +2288,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr"/>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
@@ -2094,7 +2312,7 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
@@ -2102,7 +2320,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr"/>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
@@ -2110,11 +2332,11 @@
           <t>MODULE: ERROR HANDLING &amp; EDGE CASES</t>
         </is>
       </c>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="5" t="n"/>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
+      <c r="B68" s="14" t="n"/>
+      <c r="C68" s="14" t="n"/>
+      <c r="D68" s="14" t="n"/>
+      <c r="E68" s="14" t="n"/>
+      <c r="F68" s="15" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
@@ -2134,7 +2356,7 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -2142,7 +2364,11 @@
           <t>Full Team</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr"/>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
@@ -2162,7 +2388,7 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -2170,7 +2396,11 @@
           <t>Full Team</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr"/>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
@@ -2190,7 +2420,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -2198,7 +2428,11 @@
           <t>Full Team</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr"/>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
@@ -2206,11 +2440,11 @@
           <t>MODULE: DATABASE TESTING</t>
         </is>
       </c>
-      <c r="B72" s="5" t="n"/>
-      <c r="C72" s="5" t="n"/>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="n"/>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="15" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
@@ -2230,7 +2464,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
@@ -2238,7 +2472,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr"/>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
@@ -2258,7 +2496,7 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -2266,7 +2504,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr"/>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="28" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
@@ -2274,11 +2516,11 @@
           <t>MODULE: PERFORMANCE TESTING</t>
         </is>
       </c>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="5" t="n"/>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
+      <c r="B75" s="14" t="n"/>
+      <c r="C75" s="14" t="n"/>
+      <c r="D75" s="14" t="n"/>
+      <c r="E75" s="14" t="n"/>
+      <c r="F75" s="15" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
@@ -2298,7 +2540,7 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
@@ -2306,7 +2548,11 @@
           <t>Mega</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr"/>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
@@ -2326,7 +2572,7 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -2334,7 +2580,11 @@
           <t>Mega</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr"/>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="28" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
@@ -2342,11 +2592,11 @@
           <t>MODULE: COMPATIBILITY &amp; USABILITY</t>
         </is>
       </c>
-      <c r="B78" s="5" t="n"/>
-      <c r="C78" s="5" t="n"/>
-      <c r="D78" s="5" t="n"/>
-      <c r="E78" s="5" t="n"/>
-      <c r="F78" s="5" t="n"/>
+      <c r="B78" s="14" t="n"/>
+      <c r="C78" s="14" t="n"/>
+      <c r="D78" s="14" t="n"/>
+      <c r="E78" s="14" t="n"/>
+      <c r="F78" s="15" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
@@ -2366,7 +2616,7 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
@@ -2374,7 +2624,11 @@
           <t>Kailasanathan + Mega</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr"/>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
@@ -2394,7 +2648,7 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -2402,7 +2656,11 @@
           <t>Kailasanathan + Mega</t>
         </is>
       </c>
-      <c r="F80" s="7" t="inlineStr"/>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -2422,7 +2680,7 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -2430,7 +2688,11 @@
           <t>Kailasanathan + Mega</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr"/>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
@@ -2438,11 +2700,11 @@
           <t>MODULE: EXPORT TESTING</t>
         </is>
       </c>
-      <c r="B82" s="5" t="n"/>
-      <c r="C82" s="5" t="n"/>
-      <c r="D82" s="5" t="n"/>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5" t="n"/>
+      <c r="B82" s="14" t="n"/>
+      <c r="C82" s="14" t="n"/>
+      <c r="D82" s="14" t="n"/>
+      <c r="E82" s="14" t="n"/>
+      <c r="F82" s="15" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -2462,7 +2724,7 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -2470,7 +2732,11 @@
           <t>Mega</t>
         </is>
       </c>
-      <c r="F83" s="7" t="inlineStr"/>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
@@ -2490,7 +2756,7 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -2498,7 +2764,11 @@
           <t>Mega</t>
         </is>
       </c>
-      <c r="F84" s="7" t="inlineStr"/>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="28" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -2506,11 +2776,11 @@
           <t>MODULE: ADMIN PANEL &amp; ACCOUNT</t>
         </is>
       </c>
-      <c r="B85" s="5" t="n"/>
-      <c r="C85" s="5" t="n"/>
-      <c r="D85" s="5" t="n"/>
-      <c r="E85" s="5" t="n"/>
-      <c r="F85" s="5" t="n"/>
+      <c r="B85" s="14" t="n"/>
+      <c r="C85" s="14" t="n"/>
+      <c r="D85" s="14" t="n"/>
+      <c r="E85" s="14" t="n"/>
+      <c r="F85" s="15" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
@@ -2530,7 +2800,7 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -2538,7 +2808,11 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F86" s="7" t="inlineStr"/>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
@@ -2558,7 +2832,7 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -2566,20 +2840,26 @@
           <t>Kailasanathan</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr"/>
-    </row>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>Automated pytest</t>
+        </is>
+      </c>
+    </row>
+    <row r="88"/>
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
           <t>Total Test Cases: 62 | Kailasanathan: 32 | Saagr: 11 | Mega: 13 | Full Team: 4 (Integration)</t>
         </is>
       </c>
-      <c r="B89" s="5" t="n"/>
-      <c r="C89" s="5" t="n"/>
-      <c r="D89" s="5" t="n"/>
-      <c r="E89" s="5" t="n"/>
-      <c r="F89" s="5" t="n"/>
-    </row>
+      <c r="B89" s="14" t="n"/>
+      <c r="C89" s="14" t="n"/>
+      <c r="D89" s="14" t="n"/>
+      <c r="E89" s="14" t="n"/>
+      <c r="F89" s="15" t="n"/>
+    </row>
+    <row r="90"/>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
